--- a/KatalonData/RADTestData/FEINandFEINSSNZeroError.xlsx
+++ b/KatalonData/RADTestData/FEINandFEINSSNZeroError.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3248866B-C2C5-4CAD-B64F-FBA52EE2E53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5018" yWindow="3157" windowWidth="21600" windowHeight="11326" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
+    <workbookView xWindow="6180" yWindow="2160" windowWidth="21600" windowHeight="11325" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="137">
   <si>
     <t>Result</t>
   </si>
@@ -143,36 +143,9 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fri Oct 02 19:32:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Oct 02 19:32:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Oct 02 19:32:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Oct 02 19:32:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Oct 02 19:32:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Oct 02 19:32:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Oct 02 19:32:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Oct 02 19:33:08 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Oct 02 19:47:32 EDT 2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Fri Oct 02 19:47:43 EDT 2026</t>
   </si>
   <si>
@@ -321,6 +294,159 @@
   </si>
   <si>
     <t>Fri Oct 02 19:54:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:15:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:15:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:15:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:16:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:16:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:16:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:16:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:16:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:16:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:17:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:17:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:17:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:17:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:17:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:17:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:18:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:18:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:18:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:18:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:18:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:18:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:19:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:19:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:19:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:19:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:19:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:19:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:20:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:20:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:20:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:20:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:20:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:20:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:21:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:21:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:21:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:21:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:21:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:22:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:22:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:22:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:22:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:22:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:22:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:23:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:23:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:23:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:23:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:23:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:23:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:24:03 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -728,7 +854,7 @@
         <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -741,11 +867,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s" s="1">
-        <v>45</v>
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -758,11 +884,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s" s="1">
-        <v>46</v>
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -779,7 +905,7 @@
         <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -795,11 +921,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s" s="1">
-        <v>48</v>
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -815,11 +941,11 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s" s="1">
-        <v>49</v>
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -832,11 +958,11 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s" s="1">
-        <v>50</v>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -849,11 +975,11 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s" s="1">
-        <v>51</v>
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -866,11 +992,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s" s="1">
-        <v>52</v>
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -883,11 +1009,11 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s" s="1">
-        <v>53</v>
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -903,11 +1029,11 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s" s="1">
-        <v>54</v>
+      <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -927,7 +1053,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -940,11 +1066,11 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s" s="1">
-        <v>56</v>
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -961,7 +1087,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -977,11 +1103,11 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s" s="1">
-        <v>58</v>
+      <c r="A16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -997,11 +1123,11 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s" s="1">
-        <v>59</v>
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1017,11 +1143,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s" s="1">
-        <v>60</v>
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1041,7 +1167,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1054,11 +1180,11 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B20" t="s" s="1">
-        <v>62</v>
+      <c r="A20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1075,7 +1201,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1091,11 +1217,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B22" t="s" s="1">
-        <v>64</v>
+      <c r="A22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1111,11 +1237,11 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B23" t="s" s="1">
-        <v>65</v>
+      <c r="A23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1131,11 +1257,11 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B24" t="s" s="1">
-        <v>66</v>
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1155,7 +1281,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1171,8 +1297,8 @@
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s" s="1">
-        <v>68</v>
+      <c r="B26" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1188,11 +1314,11 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A27" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s" s="1">
-        <v>69</v>
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1208,11 +1334,11 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A28" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B28" t="s" s="1">
-        <v>70</v>
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1228,11 +1354,11 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B29" t="s" s="1">
-        <v>71</v>
+      <c r="A29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1248,11 +1374,11 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A30" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B30" t="s" s="1">
-        <v>72</v>
+      <c r="A30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1265,11 +1391,11 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A31" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B31" t="s" s="1">
-        <v>73</v>
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1282,11 +1408,11 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A32" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B32" t="s" s="1">
-        <v>74</v>
+      <c r="A32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1298,12 +1424,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A33" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B33" t="s" s="1">
-        <v>75</v>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1318,12 +1444,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A34" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B34" t="s" s="1">
-        <v>76</v>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1335,12 +1461,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A35" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s" s="1">
-        <v>77</v>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1355,7 +1481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C36" s="1" t="s">
         <v>32</v>
       </c>
@@ -1369,12 +1495,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A37" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B37" t="s" s="1">
-        <v>78</v>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1386,12 +1512,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A38" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B38" t="s" s="1">
-        <v>79</v>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1403,12 +1529,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A39" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B39" t="s" s="1">
-        <v>80</v>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1420,12 +1546,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A40" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B40" t="s" s="1">
-        <v>81</v>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1437,12 +1563,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A41" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B41" t="s" s="1">
-        <v>82</v>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -1454,12 +1580,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A42" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B42" t="s" s="1">
-        <v>83</v>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1471,12 +1597,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A43" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B43" t="s" s="1">
-        <v>84</v>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1488,12 +1614,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A44" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B44" t="s" s="1">
-        <v>85</v>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1505,12 +1631,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A45" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B45" t="s" s="1">
-        <v>86</v>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1525,12 +1651,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A46" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B46" t="s" s="1">
-        <v>87</v>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1542,12 +1668,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A47" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B47" t="s" s="1">
-        <v>88</v>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1562,12 +1688,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A48" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B48" t="s" s="1">
-        <v>89</v>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1579,12 +1705,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A49" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B49" t="s" s="1">
-        <v>90</v>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1596,12 +1722,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A50" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B50" t="s" s="1">
-        <v>91</v>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1613,7 +1739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C51" s="1" t="s">
         <v>32</v>
       </c>
@@ -1627,7 +1753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C52" s="1" t="s">
         <v>32</v>
       </c>
@@ -1641,12 +1767,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A53" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B53" t="s" s="1">
-        <v>92</v>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1661,12 +1787,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A54" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B54" t="s" s="1">
-        <v>93</v>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1678,12 +1804,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.45">
-      <c r="A55" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="B55" t="s">
-        <v>94</v>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s" s="1">
+        <v>136</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
